--- a/docs/mapa-menus-modalidades-5152-5160.xlsx
+++ b/docs/mapa-menus-modalidades-5152-5160.xlsx
@@ -1,43 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Loterias\LoteriasPosicao\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110902CB-4A02-4F94-AAD2-B68957225189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F8A833-A0B3-4F01-8700-ED97F2D4BF4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Índice" sheetId="1" r:id="rId1"/>
     <sheet name="Matriz resumida" sheetId="3" r:id="rId2"/>
     <sheet name="Detalhe menus" sheetId="2" r:id="rId3"/>
-    <sheet name="5152 Lotofácil" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="5153 Super Sete" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet name="5154 Lotomania" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet name="5155 Quina" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet name="5156 Mega-Sena" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet name="5157 +Milionária" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet name="5158 Dupla Sena" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet name="5159 Timemania" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet name="5160 Dia de Sorte" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet name="Todas (uma aba)" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet name="Legenda" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet name="Faixas por Modalidade" sheetId="15" r:id="rId4"/>
+    <sheet name="5152 Lotofácil" sheetId="4" state="hidden" r:id="rId5"/>
+    <sheet name="5153 Super Sete" sheetId="5" state="hidden" r:id="rId6"/>
+    <sheet name="5154 Lotomania" sheetId="6" state="hidden" r:id="rId7"/>
+    <sheet name="5155 Quina" sheetId="7" state="hidden" r:id="rId8"/>
+    <sheet name="5156 Mega-Sena" sheetId="8" state="hidden" r:id="rId9"/>
+    <sheet name="5157 +Milionária" sheetId="9" state="hidden" r:id="rId10"/>
+    <sheet name="5158 Dupla Sena" sheetId="10" state="hidden" r:id="rId11"/>
+    <sheet name="5159 Timemania" sheetId="11" state="hidden" r:id="rId12"/>
+    <sheet name="5160 Dia de Sorte" sheetId="12" state="hidden" r:id="rId13"/>
+    <sheet name="Todas (uma aba)" sheetId="13" state="hidden" r:id="rId14"/>
+    <sheet name="Legenda" sheetId="14" state="hidden" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'5152 Lotofácil'!$A$5:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5153 Super Sete'!$A$5:$G$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5154 Lotomania'!$A$5:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'5155 Quina'!$A$5:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'5156 Mega-Sena'!$A$5:$G$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'5157 +Milionária'!$A$5:$G$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'5158 Dupla Sena'!$A$5:$G$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'5159 Timemania'!$A$5:$G$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'5160 Dia de Sorte'!$A$5:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'5152 Lotofácil'!$A$5:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5153 Super Sete'!$A$5:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'5154 Lotomania'!$A$5:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'5155 Quina'!$A$5:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'5156 Mega-Sena'!$A$5:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'5157 +Milionária'!$A$5:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'5158 Dupla Sena'!$A$5:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'5159 Timemania'!$A$5:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'5160 Dia de Sorte'!$A$5:$G$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Detalhe menus'!$A$4:$G$86</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="160">
   <si>
     <t>Mapa de menus — uma aba por modalidade (5152–5160)</t>
   </si>
@@ -532,13 +533,28 @@
   </si>
   <si>
     <t>AnalisePorPosicao--SuperSete-Only</t>
+  </si>
+  <si>
+    <t>Faixa Baixa</t>
+  </si>
+  <si>
+    <t>Faixa Média</t>
+  </si>
+  <si>
+    <t>Faixa Alta</t>
+  </si>
+  <si>
+    <t>Observações</t>
+  </si>
+  <si>
+    <t>Preencher e validar.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -602,8 +618,13 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -697,8 +718,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -745,11 +771,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -823,6 +864,13 @@
     <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -838,13 +886,16 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1148,7 +1199,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.54296875" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1156,19 +1207,19 @@
     <col min="4" max="6" width="20.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:6" ht="21">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="50" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-    </row>
-    <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+    </row>
+    <row r="2" spans="1:6" ht="16.5">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1188,7 +1239,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="16">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -1201,15 +1252,15 @@
       <c r="D3" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="E3" s="49">
+      <c r="E3" s="34">
         <v>3696</v>
       </c>
-      <c r="F3" s="48">
+      <c r="F3" s="33">
         <f>E3+1</f>
         <v>3697</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" ht="16">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -1222,15 +1273,15 @@
       <c r="D4" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="49">
+      <c r="E4" s="34">
         <v>1217</v>
       </c>
-      <c r="F4" s="48">
+      <c r="F4" s="33">
         <f t="shared" ref="F4:F11" si="0">E4+1</f>
         <v>1218</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" ht="16">
       <c r="A5" s="6" t="s">
         <v>10</v>
       </c>
@@ -1243,15 +1294,15 @@
       <c r="D5" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="34">
         <v>2929</v>
       </c>
-      <c r="F5" s="48">
+      <c r="F5" s="33">
         <f t="shared" si="0"/>
         <v>2930</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" ht="16">
       <c r="A6" s="7" t="s">
         <v>13</v>
       </c>
@@ -1264,15 +1315,15 @@
       <c r="D6" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="34">
         <v>7036</v>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="33">
         <f t="shared" si="0"/>
         <v>7037</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" ht="16">
       <c r="A7" s="8" t="s">
         <v>16</v>
       </c>
@@ -1285,15 +1336,15 @@
       <c r="D7" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="34">
         <v>3011</v>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="33">
         <f t="shared" si="0"/>
         <v>3012</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" ht="16">
       <c r="A8" s="9" t="s">
         <v>19</v>
       </c>
@@ -1306,15 +1357,15 @@
       <c r="D8" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="34">
         <v>358</v>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="33">
         <f t="shared" si="0"/>
         <v>359</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" ht="16">
       <c r="A9" s="10" t="s">
         <v>22</v>
       </c>
@@ -1327,15 +1378,15 @@
       <c r="D9" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="34">
         <v>2962</v>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="33">
         <f t="shared" si="0"/>
         <v>2963</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" ht="16">
       <c r="A10" s="11" t="s">
         <v>25</v>
       </c>
@@ -1348,15 +1399,15 @@
       <c r="D10" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="34">
         <v>2396</v>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="33">
         <f t="shared" si="0"/>
         <v>2397</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" ht="16">
       <c r="A11" s="12" t="s">
         <v>28</v>
       </c>
@@ -1369,10 +1420,10 @@
       <c r="D11" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="E11" s="49">
+      <c r="E11" s="34">
         <v>852</v>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="33">
         <f t="shared" si="0"/>
         <v>853</v>
       </c>
@@ -1386,9 +1437,282 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="39" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="6" width="32" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="21">
+      <c r="A1" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="1:7" ht="16">
+      <c r="A2" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" spans="1:7" ht="16">
+      <c r="A3" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16">
+      <c r="A6" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="20"/>
+    </row>
+    <row r="7" spans="1:7" ht="16">
+      <c r="A7" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16">
+      <c r="A8" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:7" ht="16">
+      <c r="A9" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:7" ht="16">
+      <c r="A10" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:7" ht="16">
+      <c r="A11" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16">
+      <c r="A12" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:7" ht="16">
+      <c r="A13" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:7" ht="16">
+      <c r="A14" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="20"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:G14" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1398,40 +1722,40 @@
     <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:7" ht="21">
+      <c r="A1" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-    </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="1:7" ht="16">
+      <c r="A2" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-    </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A3" s="35" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" spans="1:7" ht="16">
+      <c r="A3" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-    </row>
-    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.35">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+    </row>
+    <row r="5" spans="1:7" ht="33">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1454,7 +1778,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="16">
       <c r="A6" s="21" t="s">
         <v>22</v>
       </c>
@@ -1475,7 +1799,7 @@
       </c>
       <c r="G6" s="21"/>
     </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="16">
       <c r="A7" s="21" t="s">
         <v>22</v>
       </c>
@@ -1496,7 +1820,7 @@
       </c>
       <c r="G7" s="21"/>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="16">
       <c r="A8" s="21" t="s">
         <v>22</v>
       </c>
@@ -1517,7 +1841,7 @@
       </c>
       <c r="G8" s="21"/>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="16">
       <c r="A9" s="21" t="s">
         <v>22</v>
       </c>
@@ -1538,7 +1862,7 @@
       </c>
       <c r="G9" s="21"/>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="16">
       <c r="A10" s="21" t="s">
         <v>22</v>
       </c>
@@ -1559,7 +1883,7 @@
       </c>
       <c r="G10" s="21"/>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16">
       <c r="A11" s="21" t="s">
         <v>22</v>
       </c>
@@ -1582,7 +1906,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16">
       <c r="A12" s="21" t="s">
         <v>22</v>
       </c>
@@ -1603,7 +1927,7 @@
       </c>
       <c r="G12" s="21"/>
     </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="16">
       <c r="A13" s="21" t="s">
         <v>22</v>
       </c>
@@ -1624,7 +1948,7 @@
       </c>
       <c r="G13" s="21"/>
     </row>
-    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="16">
       <c r="A14" s="21" t="s">
         <v>22</v>
       </c>
@@ -1656,10 +1980,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1670,40 +1994,40 @@
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:7" ht="21">
+      <c r="A1" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-    </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="1:7" ht="16">
+      <c r="A2" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-    </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A3" s="35" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" spans="1:7" ht="16">
+      <c r="A3" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-    </row>
-    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.35">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+    </row>
+    <row r="5" spans="1:7" ht="33">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1726,7 +2050,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="16">
       <c r="A6" s="22" t="s">
         <v>25</v>
       </c>
@@ -1749,7 +2073,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="16">
       <c r="A7" s="22" t="s">
         <v>25</v>
       </c>
@@ -1770,7 +2094,7 @@
       </c>
       <c r="G7" s="22"/>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="16">
       <c r="A8" s="22" t="s">
         <v>25</v>
       </c>
@@ -1791,7 +2115,7 @@
       </c>
       <c r="G8" s="22"/>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="16">
       <c r="A9" s="22" t="s">
         <v>25</v>
       </c>
@@ -1814,7 +2138,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="16">
       <c r="A10" s="22" t="s">
         <v>25</v>
       </c>
@@ -1835,7 +2159,7 @@
       </c>
       <c r="G10" s="22"/>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16">
       <c r="A11" s="22" t="s">
         <v>25</v>
       </c>
@@ -1856,7 +2180,7 @@
       </c>
       <c r="G11" s="22"/>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16">
       <c r="A12" s="22" t="s">
         <v>25</v>
       </c>
@@ -1877,7 +2201,7 @@
       </c>
       <c r="G12" s="22"/>
     </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="16">
       <c r="A13" s="22" t="s">
         <v>25</v>
       </c>
@@ -1898,7 +2222,7 @@
       </c>
       <c r="G13" s="22"/>
     </row>
-    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="16">
       <c r="A14" s="22" t="s">
         <v>25</v>
       </c>
@@ -1930,10 +2254,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1944,40 +2268,40 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:7" ht="21">
+      <c r="A1" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-    </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="1:7" ht="16">
+      <c r="A2" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-    </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A3" s="35" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" spans="1:7" ht="16">
+      <c r="A3" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-    </row>
-    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.35">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+    </row>
+    <row r="5" spans="1:7" ht="33">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -2000,7 +2324,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="16">
       <c r="A6" s="23" t="s">
         <v>28</v>
       </c>
@@ -2021,7 +2345,7 @@
       </c>
       <c r="G6" s="23"/>
     </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="16">
       <c r="A7" s="23" t="s">
         <v>28</v>
       </c>
@@ -2042,7 +2366,7 @@
       </c>
       <c r="G7" s="23"/>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="16">
       <c r="A8" s="23" t="s">
         <v>28</v>
       </c>
@@ -2063,7 +2387,7 @@
       </c>
       <c r="G8" s="23"/>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="16">
       <c r="A9" s="23" t="s">
         <v>28</v>
       </c>
@@ -2084,7 +2408,7 @@
       </c>
       <c r="G9" s="23"/>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="16">
       <c r="A10" s="23" t="s">
         <v>28</v>
       </c>
@@ -2105,7 +2429,7 @@
       </c>
       <c r="G10" s="23"/>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16">
       <c r="A11" s="23" t="s">
         <v>28</v>
       </c>
@@ -2126,7 +2450,7 @@
       </c>
       <c r="G11" s="23"/>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16">
       <c r="A12" s="23" t="s">
         <v>28</v>
       </c>
@@ -2147,7 +2471,7 @@
       </c>
       <c r="G12" s="23"/>
     </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="16">
       <c r="A13" s="23" t="s">
         <v>28</v>
       </c>
@@ -2168,7 +2492,7 @@
       </c>
       <c r="G13" s="23"/>
     </row>
-    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="16">
       <c r="A14" s="23" t="s">
         <v>28</v>
       </c>
@@ -2191,7 +2515,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="16">
       <c r="A15" s="23" t="s">
         <v>28</v>
       </c>
@@ -2223,10 +2547,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:G110"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2236,29 +2560,29 @@
     <col min="7" max="7" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:7" ht="21">
+      <c r="A1" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-    </row>
-    <row r="3" spans="1:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="42" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="3" spans="1:7" ht="17.5">
+      <c r="A3" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="39"/>
-    </row>
-    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="42"/>
+    </row>
+    <row r="4" spans="1:7" ht="16.5">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -2281,7 +2605,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="16">
       <c r="A5" s="13" t="s">
         <v>4</v>
       </c>
@@ -2304,7 +2628,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="16">
       <c r="A6" s="13" t="s">
         <v>4</v>
       </c>
@@ -2327,7 +2651,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="16">
       <c r="A7" s="13" t="s">
         <v>4</v>
       </c>
@@ -2350,7 +2674,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="16">
       <c r="A8" s="13" t="s">
         <v>4</v>
       </c>
@@ -2371,7 +2695,7 @@
       </c>
       <c r="G8" s="13"/>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="16">
       <c r="A9" s="13" t="s">
         <v>4</v>
       </c>
@@ -2394,7 +2718,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="16">
       <c r="A10" s="13" t="s">
         <v>4</v>
       </c>
@@ -2417,7 +2741,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16">
       <c r="A11" s="13" t="s">
         <v>4</v>
       </c>
@@ -2440,7 +2764,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16">
       <c r="A12" s="13" t="s">
         <v>4</v>
       </c>
@@ -2461,18 +2785,18 @@
       </c>
       <c r="G12" s="13"/>
     </row>
-    <row r="14" spans="1:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="A14" s="41" t="s">
+    <row r="14" spans="1:7" ht="17.5">
+      <c r="A14" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="39"/>
-    </row>
-    <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
+    </row>
+    <row r="15" spans="1:7" ht="16.5">
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
@@ -2495,7 +2819,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="16">
       <c r="A16" s="16" t="s">
         <v>7</v>
       </c>
@@ -2516,7 +2840,7 @@
       </c>
       <c r="G16" s="16"/>
     </row>
-    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="16">
       <c r="A17" s="16" t="s">
         <v>7</v>
       </c>
@@ -2539,7 +2863,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="16">
       <c r="A18" s="16" t="s">
         <v>7</v>
       </c>
@@ -2562,7 +2886,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="16">
       <c r="A19" s="16" t="s">
         <v>7</v>
       </c>
@@ -2583,7 +2907,7 @@
       </c>
       <c r="G19" s="16"/>
     </row>
-    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="16">
       <c r="A20" s="16" t="s">
         <v>7</v>
       </c>
@@ -2604,7 +2928,7 @@
       </c>
       <c r="G20" s="16"/>
     </row>
-    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="16">
       <c r="A21" s="16" t="s">
         <v>7</v>
       </c>
@@ -2625,7 +2949,7 @@
       </c>
       <c r="G21" s="16"/>
     </row>
-    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="16">
       <c r="A22" s="16" t="s">
         <v>7</v>
       </c>
@@ -2646,7 +2970,7 @@
       </c>
       <c r="G22" s="16"/>
     </row>
-    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="16">
       <c r="A23" s="16" t="s">
         <v>7</v>
       </c>
@@ -2667,7 +2991,7 @@
       </c>
       <c r="G23" s="16"/>
     </row>
-    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="16">
       <c r="A24" s="16" t="s">
         <v>7</v>
       </c>
@@ -2688,18 +3012,18 @@
       </c>
       <c r="G24" s="16"/>
     </row>
-    <row r="26" spans="1:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="A26" s="45" t="s">
+    <row r="26" spans="1:7" ht="17.5">
+      <c r="A26" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="39"/>
-    </row>
-    <row r="27" spans="1:7" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="42"/>
+    </row>
+    <row r="27" spans="1:7" ht="16.5">
       <c r="A27" s="2" t="s">
         <v>1</v>
       </c>
@@ -2722,7 +3046,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="16">
       <c r="A28" s="17" t="s">
         <v>10</v>
       </c>
@@ -2743,7 +3067,7 @@
       </c>
       <c r="G28" s="17"/>
     </row>
-    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="16">
       <c r="A29" s="17" t="s">
         <v>10</v>
       </c>
@@ -2764,7 +3088,7 @@
       </c>
       <c r="G29" s="17"/>
     </row>
-    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="16">
       <c r="A30" s="17" t="s">
         <v>10</v>
       </c>
@@ -2785,7 +3109,7 @@
       </c>
       <c r="G30" s="17"/>
     </row>
-    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="16">
       <c r="A31" s="17" t="s">
         <v>10</v>
       </c>
@@ -2806,7 +3130,7 @@
       </c>
       <c r="G31" s="17"/>
     </row>
-    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="16">
       <c r="A32" s="17" t="s">
         <v>10</v>
       </c>
@@ -2827,7 +3151,7 @@
       </c>
       <c r="G32" s="17"/>
     </row>
-    <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="16">
       <c r="A33" s="17" t="s">
         <v>10</v>
       </c>
@@ -2848,7 +3172,7 @@
       </c>
       <c r="G33" s="17"/>
     </row>
-    <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="16">
       <c r="A34" s="17" t="s">
         <v>10</v>
       </c>
@@ -2869,7 +3193,7 @@
       </c>
       <c r="G34" s="17"/>
     </row>
-    <row r="35" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="16">
       <c r="A35" s="17" t="s">
         <v>10</v>
       </c>
@@ -2890,18 +3214,18 @@
       </c>
       <c r="G35" s="17"/>
     </row>
-    <row r="37" spans="1:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="A37" s="40" t="s">
+    <row r="37" spans="1:7" ht="17.5">
+      <c r="A37" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="39"/>
-    </row>
-    <row r="38" spans="1:7" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B37" s="41"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="42"/>
+    </row>
+    <row r="38" spans="1:7" ht="16.5">
       <c r="A38" s="2" t="s">
         <v>1</v>
       </c>
@@ -2924,7 +3248,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="16">
       <c r="A39" s="18" t="s">
         <v>13</v>
       </c>
@@ -2945,7 +3269,7 @@
       </c>
       <c r="G39" s="18"/>
     </row>
-    <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" ht="16">
       <c r="A40" s="18" t="s">
         <v>13</v>
       </c>
@@ -2966,7 +3290,7 @@
       </c>
       <c r="G40" s="18"/>
     </row>
-    <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" ht="16">
       <c r="A41" s="18" t="s">
         <v>13</v>
       </c>
@@ -2987,7 +3311,7 @@
       </c>
       <c r="G41" s="18"/>
     </row>
-    <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="16">
       <c r="A42" s="18" t="s">
         <v>13</v>
       </c>
@@ -3008,7 +3332,7 @@
       </c>
       <c r="G42" s="18"/>
     </row>
-    <row r="43" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" ht="16">
       <c r="A43" s="18" t="s">
         <v>13</v>
       </c>
@@ -3029,7 +3353,7 @@
       </c>
       <c r="G43" s="18"/>
     </row>
-    <row r="44" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" ht="16">
       <c r="A44" s="18" t="s">
         <v>13</v>
       </c>
@@ -3050,7 +3374,7 @@
       </c>
       <c r="G44" s="18"/>
     </row>
-    <row r="45" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" ht="16">
       <c r="A45" s="18" t="s">
         <v>13</v>
       </c>
@@ -3071,7 +3395,7 @@
       </c>
       <c r="G45" s="18"/>
     </row>
-    <row r="46" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" ht="16">
       <c r="A46" s="18" t="s">
         <v>13</v>
       </c>
@@ -3092,18 +3416,18 @@
       </c>
       <c r="G46" s="18"/>
     </row>
-    <row r="48" spans="1:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="A48" s="44" t="s">
+    <row r="48" spans="1:7" ht="17.5">
+      <c r="A48" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="B48" s="38"/>
-      <c r="C48" s="38"/>
-      <c r="D48" s="38"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="39"/>
-    </row>
-    <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B48" s="41"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="42"/>
+    </row>
+    <row r="49" spans="1:7" ht="16.5">
       <c r="A49" s="2" t="s">
         <v>1</v>
       </c>
@@ -3126,7 +3450,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" ht="16">
       <c r="A50" s="19" t="s">
         <v>16</v>
       </c>
@@ -3147,7 +3471,7 @@
       </c>
       <c r="G50" s="19"/>
     </row>
-    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" ht="16">
       <c r="A51" s="19" t="s">
         <v>16</v>
       </c>
@@ -3168,7 +3492,7 @@
       </c>
       <c r="G51" s="19"/>
     </row>
-    <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" ht="16">
       <c r="A52" s="19" t="s">
         <v>16</v>
       </c>
@@ -3189,7 +3513,7 @@
       </c>
       <c r="G52" s="19"/>
     </row>
-    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" ht="16">
       <c r="A53" s="19" t="s">
         <v>16</v>
       </c>
@@ -3210,7 +3534,7 @@
       </c>
       <c r="G53" s="19"/>
     </row>
-    <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" ht="16">
       <c r="A54" s="19" t="s">
         <v>16</v>
       </c>
@@ -3231,7 +3555,7 @@
       </c>
       <c r="G54" s="19"/>
     </row>
-    <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" ht="16">
       <c r="A55" s="19" t="s">
         <v>16</v>
       </c>
@@ -3254,7 +3578,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" ht="16">
       <c r="A56" s="19" t="s">
         <v>16</v>
       </c>
@@ -3277,7 +3601,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" ht="16">
       <c r="A57" s="19" t="s">
         <v>16</v>
       </c>
@@ -3298,7 +3622,7 @@
       </c>
       <c r="G57" s="19"/>
     </row>
-    <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" ht="16">
       <c r="A58" s="19" t="s">
         <v>16</v>
       </c>
@@ -3319,7 +3643,7 @@
       </c>
       <c r="G58" s="19"/>
     </row>
-    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" ht="16">
       <c r="A59" s="19" t="s">
         <v>16</v>
       </c>
@@ -3340,7 +3664,7 @@
       </c>
       <c r="G59" s="19"/>
     </row>
-    <row r="60" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" ht="16">
       <c r="A60" s="19" t="s">
         <v>16</v>
       </c>
@@ -3361,7 +3685,7 @@
       </c>
       <c r="G60" s="19"/>
     </row>
-    <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" ht="16">
       <c r="A61" s="19" t="s">
         <v>16</v>
       </c>
@@ -3382,18 +3706,18 @@
       </c>
       <c r="G61" s="19"/>
     </row>
-    <row r="63" spans="1:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="A63" s="47" t="s">
+    <row r="63" spans="1:7" ht="17.5">
+      <c r="A63" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="B63" s="38"/>
-      <c r="C63" s="38"/>
-      <c r="D63" s="38"/>
-      <c r="E63" s="38"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="39"/>
-    </row>
-    <row r="64" spans="1:7" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B63" s="41"/>
+      <c r="C63" s="41"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="41"/>
+      <c r="G63" s="42"/>
+    </row>
+    <row r="64" spans="1:7" ht="16.5">
       <c r="A64" s="2" t="s">
         <v>1</v>
       </c>
@@ -3416,7 +3740,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" ht="16">
       <c r="A65" s="20" t="s">
         <v>19</v>
       </c>
@@ -3437,7 +3761,7 @@
       </c>
       <c r="G65" s="20"/>
     </row>
-    <row r="66" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" ht="16">
       <c r="A66" s="20" t="s">
         <v>19</v>
       </c>
@@ -3460,7 +3784,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" ht="16">
       <c r="A67" s="20" t="s">
         <v>19</v>
       </c>
@@ -3481,7 +3805,7 @@
       </c>
       <c r="G67" s="20"/>
     </row>
-    <row r="68" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" ht="16">
       <c r="A68" s="20" t="s">
         <v>19</v>
       </c>
@@ -3502,7 +3826,7 @@
       </c>
       <c r="G68" s="20"/>
     </row>
-    <row r="69" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" ht="16">
       <c r="A69" s="20" t="s">
         <v>19</v>
       </c>
@@ -3523,7 +3847,7 @@
       </c>
       <c r="G69" s="20"/>
     </row>
-    <row r="70" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" ht="16">
       <c r="A70" s="20" t="s">
         <v>19</v>
       </c>
@@ -3546,7 +3870,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" ht="16">
       <c r="A71" s="20" t="s">
         <v>19</v>
       </c>
@@ -3567,7 +3891,7 @@
       </c>
       <c r="G71" s="20"/>
     </row>
-    <row r="72" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" ht="16">
       <c r="A72" s="20" t="s">
         <v>19</v>
       </c>
@@ -3588,7 +3912,7 @@
       </c>
       <c r="G72" s="20"/>
     </row>
-    <row r="73" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" ht="16">
       <c r="A73" s="20" t="s">
         <v>19</v>
       </c>
@@ -3609,18 +3933,18 @@
       </c>
       <c r="G73" s="20"/>
     </row>
-    <row r="75" spans="1:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="A75" s="46" t="s">
+    <row r="75" spans="1:7" ht="17.5">
+      <c r="A75" s="49" t="s">
         <v>133</v>
       </c>
-      <c r="B75" s="38"/>
-      <c r="C75" s="38"/>
-      <c r="D75" s="38"/>
-      <c r="E75" s="38"/>
-      <c r="F75" s="38"/>
-      <c r="G75" s="39"/>
-    </row>
-    <row r="76" spans="1:7" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B75" s="41"/>
+      <c r="C75" s="41"/>
+      <c r="D75" s="41"/>
+      <c r="E75" s="41"/>
+      <c r="F75" s="41"/>
+      <c r="G75" s="42"/>
+    </row>
+    <row r="76" spans="1:7" ht="16.5">
       <c r="A76" s="2" t="s">
         <v>1</v>
       </c>
@@ -3643,7 +3967,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" ht="16">
       <c r="A77" s="21" t="s">
         <v>22</v>
       </c>
@@ -3664,7 +3988,7 @@
       </c>
       <c r="G77" s="21"/>
     </row>
-    <row r="78" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" ht="16">
       <c r="A78" s="21" t="s">
         <v>22</v>
       </c>
@@ -3685,7 +4009,7 @@
       </c>
       <c r="G78" s="21"/>
     </row>
-    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" ht="16">
       <c r="A79" s="21" t="s">
         <v>22</v>
       </c>
@@ -3706,7 +4030,7 @@
       </c>
       <c r="G79" s="21"/>
     </row>
-    <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" ht="16">
       <c r="A80" s="21" t="s">
         <v>22</v>
       </c>
@@ -3727,7 +4051,7 @@
       </c>
       <c r="G80" s="21"/>
     </row>
-    <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" ht="16">
       <c r="A81" s="21" t="s">
         <v>22</v>
       </c>
@@ -3748,7 +4072,7 @@
       </c>
       <c r="G81" s="21"/>
     </row>
-    <row r="82" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" ht="16">
       <c r="A82" s="21" t="s">
         <v>22</v>
       </c>
@@ -3771,7 +4095,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" ht="16">
       <c r="A83" s="21" t="s">
         <v>22</v>
       </c>
@@ -3792,7 +4116,7 @@
       </c>
       <c r="G83" s="21"/>
     </row>
-    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" ht="16">
       <c r="A84" s="21" t="s">
         <v>22</v>
       </c>
@@ -3813,7 +4137,7 @@
       </c>
       <c r="G84" s="21"/>
     </row>
-    <row r="85" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" ht="16">
       <c r="A85" s="21" t="s">
         <v>22</v>
       </c>
@@ -3834,18 +4158,18 @@
       </c>
       <c r="G85" s="21"/>
     </row>
-    <row r="87" spans="1:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="A87" s="43" t="s">
+    <row r="87" spans="1:7" ht="17.5">
+      <c r="A87" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="B87" s="38"/>
-      <c r="C87" s="38"/>
-      <c r="D87" s="38"/>
-      <c r="E87" s="38"/>
-      <c r="F87" s="38"/>
-      <c r="G87" s="39"/>
-    </row>
-    <row r="88" spans="1:7" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B87" s="41"/>
+      <c r="C87" s="41"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="41"/>
+      <c r="F87" s="41"/>
+      <c r="G87" s="42"/>
+    </row>
+    <row r="88" spans="1:7" ht="16.5">
       <c r="A88" s="2" t="s">
         <v>1</v>
       </c>
@@ -3868,7 +4192,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" ht="16">
       <c r="A89" s="22" t="s">
         <v>25</v>
       </c>
@@ -3891,7 +4215,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" ht="16">
       <c r="A90" s="22" t="s">
         <v>25</v>
       </c>
@@ -3912,7 +4236,7 @@
       </c>
       <c r="G90" s="22"/>
     </row>
-    <row r="91" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" ht="16">
       <c r="A91" s="22" t="s">
         <v>25</v>
       </c>
@@ -3933,7 +4257,7 @@
       </c>
       <c r="G91" s="22"/>
     </row>
-    <row r="92" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" ht="16">
       <c r="A92" s="22" t="s">
         <v>25</v>
       </c>
@@ -3956,7 +4280,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" ht="16">
       <c r="A93" s="22" t="s">
         <v>25</v>
       </c>
@@ -3977,7 +4301,7 @@
       </c>
       <c r="G93" s="22"/>
     </row>
-    <row r="94" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" ht="16">
       <c r="A94" s="22" t="s">
         <v>25</v>
       </c>
@@ -3998,7 +4322,7 @@
       </c>
       <c r="G94" s="22"/>
     </row>
-    <row r="95" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" ht="16">
       <c r="A95" s="22" t="s">
         <v>25</v>
       </c>
@@ -4019,7 +4343,7 @@
       </c>
       <c r="G95" s="22"/>
     </row>
-    <row r="96" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" ht="16">
       <c r="A96" s="22" t="s">
         <v>25</v>
       </c>
@@ -4040,7 +4364,7 @@
       </c>
       <c r="G96" s="22"/>
     </row>
-    <row r="97" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" ht="16">
       <c r="A97" s="22" t="s">
         <v>25</v>
       </c>
@@ -4061,18 +4385,18 @@
       </c>
       <c r="G97" s="22"/>
     </row>
-    <row r="99" spans="1:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="A99" s="37" t="s">
+    <row r="99" spans="1:7" ht="17.5">
+      <c r="A99" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="B99" s="38"/>
-      <c r="C99" s="38"/>
-      <c r="D99" s="38"/>
-      <c r="E99" s="38"/>
-      <c r="F99" s="38"/>
-      <c r="G99" s="39"/>
-    </row>
-    <row r="100" spans="1:7" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B99" s="41"/>
+      <c r="C99" s="41"/>
+      <c r="D99" s="41"/>
+      <c r="E99" s="41"/>
+      <c r="F99" s="41"/>
+      <c r="G99" s="42"/>
+    </row>
+    <row r="100" spans="1:7" ht="16.5">
       <c r="A100" s="2" t="s">
         <v>1</v>
       </c>
@@ -4095,7 +4419,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" ht="16">
       <c r="A101" s="23" t="s">
         <v>28</v>
       </c>
@@ -4116,7 +4440,7 @@
       </c>
       <c r="G101" s="23"/>
     </row>
-    <row r="102" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" ht="16">
       <c r="A102" s="23" t="s">
         <v>28</v>
       </c>
@@ -4137,7 +4461,7 @@
       </c>
       <c r="G102" s="23"/>
     </row>
-    <row r="103" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" ht="16">
       <c r="A103" s="23" t="s">
         <v>28</v>
       </c>
@@ -4158,7 +4482,7 @@
       </c>
       <c r="G103" s="23"/>
     </row>
-    <row r="104" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" ht="16">
       <c r="A104" s="23" t="s">
         <v>28</v>
       </c>
@@ -4179,7 +4503,7 @@
       </c>
       <c r="G104" s="23"/>
     </row>
-    <row r="105" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" ht="16">
       <c r="A105" s="23" t="s">
         <v>28</v>
       </c>
@@ -4200,7 +4524,7 @@
       </c>
       <c r="G105" s="23"/>
     </row>
-    <row r="106" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" ht="16">
       <c r="A106" s="23" t="s">
         <v>28</v>
       </c>
@@ -4221,7 +4545,7 @@
       </c>
       <c r="G106" s="23"/>
     </row>
-    <row r="107" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" ht="16">
       <c r="A107" s="23" t="s">
         <v>28</v>
       </c>
@@ -4242,7 +4566,7 @@
       </c>
       <c r="G107" s="23"/>
     </row>
-    <row r="108" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" ht="16">
       <c r="A108" s="23" t="s">
         <v>28</v>
       </c>
@@ -4263,7 +4587,7 @@
       </c>
       <c r="G108" s="23"/>
     </row>
-    <row r="109" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" ht="16">
       <c r="A109" s="23" t="s">
         <v>28</v>
       </c>
@@ -4286,7 +4610,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" ht="16">
       <c r="A110" s="23" t="s">
         <v>28</v>
       </c>
@@ -4324,21 +4648,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="21">
       <c r="A1" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" ht="17.5">
       <c r="A3" s="29" t="s">
         <v>114</v>
       </c>
@@ -4346,7 +4670,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" ht="17.5">
       <c r="A4" s="29" t="s">
         <v>120</v>
       </c>
@@ -4354,7 +4678,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" ht="17.5">
       <c r="A5" s="29" t="s">
         <v>121</v>
       </c>
@@ -4362,7 +4686,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" ht="17.5">
       <c r="A6" s="29" t="s">
         <v>122</v>
       </c>
@@ -4370,13 +4694,13 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" ht="17.5">
       <c r="A7" s="29"/>
       <c r="B7" s="30" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" ht="17.5">
       <c r="A8" s="29"/>
       <c r="B8" s="30" t="s">
         <v>143</v>
@@ -4390,7 +4714,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -4404,35 +4728,35 @@
     <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:10" ht="21">
+      <c r="A1" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-    </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.45">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+    </row>
+    <row r="2" spans="1:10" ht="16">
+      <c r="A2" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-    </row>
-    <row r="4" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+    </row>
+    <row r="4" spans="1:10" ht="36" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>105</v>
       </c>
@@ -4464,7 +4788,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="28" customHeight="1">
       <c r="A5" s="24" t="s">
         <v>113</v>
       </c>
@@ -4496,7 +4820,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="28" customHeight="1">
       <c r="A6" s="26" t="s">
         <v>115</v>
       </c>
@@ -4512,7 +4836,7 @@
       <c r="I6" s="27"/>
       <c r="J6" s="27"/>
     </row>
-    <row r="7" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="28" customHeight="1">
       <c r="A7" s="24" t="s">
         <v>116</v>
       </c>
@@ -4528,7 +4852,7 @@
       <c r="I7" s="27"/>
       <c r="J7" s="27"/>
     </row>
-    <row r="8" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="28" customHeight="1">
       <c r="A8" s="26" t="s">
         <v>117</v>
       </c>
@@ -4560,7 +4884,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="28" customHeight="1">
       <c r="A9" s="24" t="s">
         <v>118</v>
       </c>
@@ -4576,7 +4900,7 @@
       </c>
       <c r="J9" s="27"/>
     </row>
-    <row r="10" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="28" customHeight="1">
       <c r="A10" s="26" t="s">
         <v>119</v>
       </c>
@@ -4598,7 +4922,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="28" customHeight="1">
       <c r="A11" s="24" t="s">
         <v>123</v>
       </c>
@@ -4628,7 +4952,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="28" customHeight="1">
       <c r="A12" s="26" t="s">
         <v>124</v>
       </c>
@@ -4660,7 +4984,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="28" customHeight="1">
       <c r="A13" s="24" t="s">
         <v>100</v>
       </c>
@@ -4676,7 +5000,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="28" customHeight="1">
       <c r="A14" s="26" t="s">
         <v>125</v>
       </c>
@@ -4720,7 +5044,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G86"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -4730,29 +5054,29 @@
     <col min="7" max="7" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:7" ht="21">
+      <c r="A1" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-    </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="1:7" ht="16">
+      <c r="A2" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-    </row>
-    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="4" spans="1:7" ht="16.5">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -4775,7 +5099,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="16">
       <c r="A5" s="13" t="s">
         <v>4</v>
       </c>
@@ -4798,7 +5122,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="16">
       <c r="A6" s="13" t="s">
         <v>4</v>
       </c>
@@ -4821,7 +5145,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="16">
       <c r="A7" s="13" t="s">
         <v>4</v>
       </c>
@@ -4844,7 +5168,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="16">
       <c r="A8" s="13" t="s">
         <v>4</v>
       </c>
@@ -4865,7 +5189,7 @@
       </c>
       <c r="G8" s="15"/>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="16">
       <c r="A9" s="13" t="s">
         <v>4</v>
       </c>
@@ -4888,7 +5212,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="16">
       <c r="A10" s="13" t="s">
         <v>4</v>
       </c>
@@ -4911,7 +5235,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16">
       <c r="A11" s="13" t="s">
         <v>4</v>
       </c>
@@ -4934,7 +5258,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16">
       <c r="A12" s="13" t="s">
         <v>4</v>
       </c>
@@ -4955,7 +5279,7 @@
       </c>
       <c r="G12" s="15"/>
     </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="16">
       <c r="A13" s="16" t="s">
         <v>7</v>
       </c>
@@ -4976,7 +5300,7 @@
       </c>
       <c r="G13" s="14"/>
     </row>
-    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="16">
       <c r="A14" s="16" t="s">
         <v>7</v>
       </c>
@@ -4999,7 +5323,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="16">
       <c r="A15" s="16" t="s">
         <v>7</v>
       </c>
@@ -5022,7 +5346,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="16">
       <c r="A16" s="16" t="s">
         <v>7</v>
       </c>
@@ -5043,7 +5367,7 @@
       </c>
       <c r="G16" s="15"/>
     </row>
-    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="16">
       <c r="A17" s="16" t="s">
         <v>7</v>
       </c>
@@ -5064,7 +5388,7 @@
       </c>
       <c r="G17" s="14"/>
     </row>
-    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="16">
       <c r="A18" s="16" t="s">
         <v>7</v>
       </c>
@@ -5085,7 +5409,7 @@
       </c>
       <c r="G18" s="15"/>
     </row>
-    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="16">
       <c r="A19" s="16" t="s">
         <v>7</v>
       </c>
@@ -5106,7 +5430,7 @@
       </c>
       <c r="G19" s="14"/>
     </row>
-    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="16">
       <c r="A20" s="16" t="s">
         <v>7</v>
       </c>
@@ -5127,7 +5451,7 @@
       </c>
       <c r="G20" s="15"/>
     </row>
-    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="16">
       <c r="A21" s="16" t="s">
         <v>7</v>
       </c>
@@ -5148,7 +5472,7 @@
       </c>
       <c r="G21" s="14"/>
     </row>
-    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="16">
       <c r="A22" s="17" t="s">
         <v>10</v>
       </c>
@@ -5169,7 +5493,7 @@
       </c>
       <c r="G22" s="15"/>
     </row>
-    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="16">
       <c r="A23" s="17" t="s">
         <v>10</v>
       </c>
@@ -5190,7 +5514,7 @@
       </c>
       <c r="G23" s="14"/>
     </row>
-    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="16">
       <c r="A24" s="17" t="s">
         <v>10</v>
       </c>
@@ -5211,7 +5535,7 @@
       </c>
       <c r="G24" s="15"/>
     </row>
-    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="16">
       <c r="A25" s="17" t="s">
         <v>10</v>
       </c>
@@ -5232,7 +5556,7 @@
       </c>
       <c r="G25" s="14"/>
     </row>
-    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="16">
       <c r="A26" s="17" t="s">
         <v>10</v>
       </c>
@@ -5253,7 +5577,7 @@
       </c>
       <c r="G26" s="15"/>
     </row>
-    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="16">
       <c r="A27" s="17" t="s">
         <v>10</v>
       </c>
@@ -5274,7 +5598,7 @@
       </c>
       <c r="G27" s="14"/>
     </row>
-    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="16">
       <c r="A28" s="17" t="s">
         <v>10</v>
       </c>
@@ -5295,7 +5619,7 @@
       </c>
       <c r="G28" s="15"/>
     </row>
-    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="16">
       <c r="A29" s="17" t="s">
         <v>10</v>
       </c>
@@ -5316,7 +5640,7 @@
       </c>
       <c r="G29" s="14"/>
     </row>
-    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="16">
       <c r="A30" s="18" t="s">
         <v>13</v>
       </c>
@@ -5337,7 +5661,7 @@
       </c>
       <c r="G30" s="15"/>
     </row>
-    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="16">
       <c r="A31" s="18" t="s">
         <v>13</v>
       </c>
@@ -5358,7 +5682,7 @@
       </c>
       <c r="G31" s="14"/>
     </row>
-    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="16">
       <c r="A32" s="18" t="s">
         <v>13</v>
       </c>
@@ -5379,7 +5703,7 @@
       </c>
       <c r="G32" s="15"/>
     </row>
-    <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="16">
       <c r="A33" s="18" t="s">
         <v>13</v>
       </c>
@@ -5400,7 +5724,7 @@
       </c>
       <c r="G33" s="14"/>
     </row>
-    <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="16">
       <c r="A34" s="18" t="s">
         <v>13</v>
       </c>
@@ -5421,7 +5745,7 @@
       </c>
       <c r="G34" s="15"/>
     </row>
-    <row r="35" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="16">
       <c r="A35" s="18" t="s">
         <v>13</v>
       </c>
@@ -5442,7 +5766,7 @@
       </c>
       <c r="G35" s="14"/>
     </row>
-    <row r="36" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" ht="16">
       <c r="A36" s="18" t="s">
         <v>13</v>
       </c>
@@ -5463,7 +5787,7 @@
       </c>
       <c r="G36" s="15"/>
     </row>
-    <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="16">
       <c r="A37" s="18" t="s">
         <v>13</v>
       </c>
@@ -5484,7 +5808,7 @@
       </c>
       <c r="G37" s="14"/>
     </row>
-    <row r="38" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="16">
       <c r="A38" s="19" t="s">
         <v>16</v>
       </c>
@@ -5505,7 +5829,7 @@
       </c>
       <c r="G38" s="15"/>
     </row>
-    <row r="39" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="16">
       <c r="A39" s="19" t="s">
         <v>16</v>
       </c>
@@ -5526,7 +5850,7 @@
       </c>
       <c r="G39" s="14"/>
     </row>
-    <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" ht="16">
       <c r="A40" s="19" t="s">
         <v>16</v>
       </c>
@@ -5547,7 +5871,7 @@
       </c>
       <c r="G40" s="15"/>
     </row>
-    <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" ht="16">
       <c r="A41" s="19" t="s">
         <v>16</v>
       </c>
@@ -5568,7 +5892,7 @@
       </c>
       <c r="G41" s="14"/>
     </row>
-    <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="16">
       <c r="A42" s="19" t="s">
         <v>16</v>
       </c>
@@ -5589,7 +5913,7 @@
       </c>
       <c r="G42" s="15"/>
     </row>
-    <row r="43" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" ht="16">
       <c r="A43" s="19" t="s">
         <v>16</v>
       </c>
@@ -5612,7 +5936,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" ht="16">
       <c r="A44" s="19" t="s">
         <v>16</v>
       </c>
@@ -5635,7 +5959,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" ht="16">
       <c r="A45" s="19" t="s">
         <v>16</v>
       </c>
@@ -5656,7 +5980,7 @@
       </c>
       <c r="G45" s="14"/>
     </row>
-    <row r="46" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" ht="16">
       <c r="A46" s="19" t="s">
         <v>16</v>
       </c>
@@ -5677,7 +6001,7 @@
       </c>
       <c r="G46" s="15"/>
     </row>
-    <row r="47" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" ht="16">
       <c r="A47" s="19" t="s">
         <v>16</v>
       </c>
@@ -5698,7 +6022,7 @@
       </c>
       <c r="G47" s="14"/>
     </row>
-    <row r="48" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" ht="16">
       <c r="A48" s="19" t="s">
         <v>16</v>
       </c>
@@ -5719,7 +6043,7 @@
       </c>
       <c r="G48" s="15"/>
     </row>
-    <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" ht="16">
       <c r="A49" s="19" t="s">
         <v>16</v>
       </c>
@@ -5740,7 +6064,7 @@
       </c>
       <c r="G49" s="14"/>
     </row>
-    <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" ht="16">
       <c r="A50" s="20" t="s">
         <v>19</v>
       </c>
@@ -5761,7 +6085,7 @@
       </c>
       <c r="G50" s="15"/>
     </row>
-    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" ht="16">
       <c r="A51" s="20" t="s">
         <v>19</v>
       </c>
@@ -5784,7 +6108,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" ht="16">
       <c r="A52" s="20" t="s">
         <v>19</v>
       </c>
@@ -5805,7 +6129,7 @@
       </c>
       <c r="G52" s="15"/>
     </row>
-    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" ht="16">
       <c r="A53" s="20" t="s">
         <v>19</v>
       </c>
@@ -5826,7 +6150,7 @@
       </c>
       <c r="G53" s="14"/>
     </row>
-    <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" ht="16">
       <c r="A54" s="20" t="s">
         <v>19</v>
       </c>
@@ -5847,7 +6171,7 @@
       </c>
       <c r="G54" s="15"/>
     </row>
-    <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" ht="16">
       <c r="A55" s="20" t="s">
         <v>19</v>
       </c>
@@ -5870,7 +6194,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" ht="16">
       <c r="A56" s="20" t="s">
         <v>19</v>
       </c>
@@ -5891,7 +6215,7 @@
       </c>
       <c r="G56" s="15"/>
     </row>
-    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" ht="16">
       <c r="A57" s="20" t="s">
         <v>19</v>
       </c>
@@ -5912,7 +6236,7 @@
       </c>
       <c r="G57" s="14"/>
     </row>
-    <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" ht="16">
       <c r="A58" s="20" t="s">
         <v>19</v>
       </c>
@@ -5933,7 +6257,7 @@
       </c>
       <c r="G58" s="15"/>
     </row>
-    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" ht="16">
       <c r="A59" s="21" t="s">
         <v>22</v>
       </c>
@@ -5954,7 +6278,7 @@
       </c>
       <c r="G59" s="14"/>
     </row>
-    <row r="60" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" ht="16">
       <c r="A60" s="21" t="s">
         <v>22</v>
       </c>
@@ -5975,7 +6299,7 @@
       </c>
       <c r="G60" s="15"/>
     </row>
-    <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" ht="16">
       <c r="A61" s="21" t="s">
         <v>22</v>
       </c>
@@ -5996,7 +6320,7 @@
       </c>
       <c r="G61" s="14"/>
     </row>
-    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" ht="16">
       <c r="A62" s="21" t="s">
         <v>22</v>
       </c>
@@ -6017,7 +6341,7 @@
       </c>
       <c r="G62" s="15"/>
     </row>
-    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" ht="16">
       <c r="A63" s="21" t="s">
         <v>22</v>
       </c>
@@ -6038,7 +6362,7 @@
       </c>
       <c r="G63" s="14"/>
     </row>
-    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" ht="16">
       <c r="A64" s="21" t="s">
         <v>22</v>
       </c>
@@ -6061,7 +6385,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" ht="16">
       <c r="A65" s="21" t="s">
         <v>22</v>
       </c>
@@ -6082,7 +6406,7 @@
       </c>
       <c r="G65" s="14"/>
     </row>
-    <row r="66" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" ht="16">
       <c r="A66" s="21" t="s">
         <v>22</v>
       </c>
@@ -6103,7 +6427,7 @@
       </c>
       <c r="G66" s="15"/>
     </row>
-    <row r="67" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" ht="16">
       <c r="A67" s="21" t="s">
         <v>22</v>
       </c>
@@ -6124,7 +6448,7 @@
       </c>
       <c r="G67" s="14"/>
     </row>
-    <row r="68" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" ht="16">
       <c r="A68" s="22" t="s">
         <v>25</v>
       </c>
@@ -6147,7 +6471,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" ht="16">
       <c r="A69" s="22" t="s">
         <v>25</v>
       </c>
@@ -6168,7 +6492,7 @@
       </c>
       <c r="G69" s="14"/>
     </row>
-    <row r="70" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" ht="16">
       <c r="A70" s="22" t="s">
         <v>25</v>
       </c>
@@ -6189,7 +6513,7 @@
       </c>
       <c r="G70" s="15"/>
     </row>
-    <row r="71" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" ht="16">
       <c r="A71" s="22" t="s">
         <v>25</v>
       </c>
@@ -6212,7 +6536,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" ht="16">
       <c r="A72" s="22" t="s">
         <v>25</v>
       </c>
@@ -6233,7 +6557,7 @@
       </c>
       <c r="G72" s="15"/>
     </row>
-    <row r="73" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" ht="16">
       <c r="A73" s="22" t="s">
         <v>25</v>
       </c>
@@ -6254,7 +6578,7 @@
       </c>
       <c r="G73" s="14"/>
     </row>
-    <row r="74" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" ht="16">
       <c r="A74" s="22" t="s">
         <v>25</v>
       </c>
@@ -6275,7 +6599,7 @@
       </c>
       <c r="G74" s="15"/>
     </row>
-    <row r="75" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" ht="16">
       <c r="A75" s="22" t="s">
         <v>25</v>
       </c>
@@ -6296,7 +6620,7 @@
       </c>
       <c r="G75" s="14"/>
     </row>
-    <row r="76" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" ht="16">
       <c r="A76" s="22" t="s">
         <v>25</v>
       </c>
@@ -6317,7 +6641,7 @@
       </c>
       <c r="G76" s="15"/>
     </row>
-    <row r="77" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" ht="16">
       <c r="A77" s="23" t="s">
         <v>28</v>
       </c>
@@ -6338,7 +6662,7 @@
       </c>
       <c r="G77" s="14"/>
     </row>
-    <row r="78" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" ht="16">
       <c r="A78" s="23" t="s">
         <v>28</v>
       </c>
@@ -6359,7 +6683,7 @@
       </c>
       <c r="G78" s="15"/>
     </row>
-    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" ht="16">
       <c r="A79" s="23" t="s">
         <v>28</v>
       </c>
@@ -6380,7 +6704,7 @@
       </c>
       <c r="G79" s="14"/>
     </row>
-    <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" ht="16">
       <c r="A80" s="23" t="s">
         <v>28</v>
       </c>
@@ -6401,7 +6725,7 @@
       </c>
       <c r="G80" s="15"/>
     </row>
-    <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" ht="16">
       <c r="A81" s="23" t="s">
         <v>28</v>
       </c>
@@ -6422,7 +6746,7 @@
       </c>
       <c r="G81" s="14"/>
     </row>
-    <row r="82" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" ht="16">
       <c r="A82" s="23" t="s">
         <v>28</v>
       </c>
@@ -6443,7 +6767,7 @@
       </c>
       <c r="G82" s="15"/>
     </row>
-    <row r="83" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" ht="16">
       <c r="A83" s="23" t="s">
         <v>28</v>
       </c>
@@ -6464,7 +6788,7 @@
       </c>
       <c r="G83" s="14"/>
     </row>
-    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" ht="16">
       <c r="A84" s="23" t="s">
         <v>28</v>
       </c>
@@ -6485,7 +6809,7 @@
       </c>
       <c r="G84" s="15"/>
     </row>
-    <row r="85" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" ht="16">
       <c r="A85" s="23" t="s">
         <v>28</v>
       </c>
@@ -6508,7 +6832,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" ht="16">
       <c r="A86" s="23" t="s">
         <v>28</v>
       </c>
@@ -6540,9 +6864,140 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{740D562A-5C99-4F85-B144-30281B351756}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="22" customHeight="1">
+      <c r="A1" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="52" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -6552,40 +7007,40 @@
     <col min="7" max="7" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:7" ht="21">
+      <c r="A1" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-    </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="1:7" ht="16">
+      <c r="A2" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-    </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A3" s="35" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" spans="1:7" ht="16">
+      <c r="A3" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-    </row>
-    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.35">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+    </row>
+    <row r="5" spans="1:7" ht="33">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -6608,7 +7063,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="16">
       <c r="A6" s="13" t="s">
         <v>4</v>
       </c>
@@ -6631,7 +7086,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="16">
       <c r="A7" s="13" t="s">
         <v>4</v>
       </c>
@@ -6654,7 +7109,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="16">
       <c r="A8" s="13" t="s">
         <v>4</v>
       </c>
@@ -6677,7 +7132,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="16">
       <c r="A9" s="13" t="s">
         <v>4</v>
       </c>
@@ -6698,7 +7153,7 @@
       </c>
       <c r="G9" s="13"/>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="16">
       <c r="A10" s="13" t="s">
         <v>4</v>
       </c>
@@ -6721,7 +7176,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16">
       <c r="A11" s="13" t="s">
         <v>4</v>
       </c>
@@ -6744,7 +7199,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16">
       <c r="A12" s="13" t="s">
         <v>4</v>
       </c>
@@ -6767,7 +7222,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="16">
       <c r="A13" s="13" t="s">
         <v>4</v>
       </c>
@@ -6799,10 +7254,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -6812,40 +7267,40 @@
     <col min="7" max="7" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:7" ht="21">
+      <c r="A1" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-    </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="1:7" ht="16">
+      <c r="A2" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-    </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A3" s="35" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" spans="1:7" ht="16">
+      <c r="A3" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-    </row>
-    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.35">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+    </row>
+    <row r="5" spans="1:7" ht="33">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -6868,7 +7323,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="16">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -6889,7 +7344,7 @@
       </c>
       <c r="G6" s="16"/>
     </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="16">
       <c r="A7" s="16" t="s">
         <v>7</v>
       </c>
@@ -6912,7 +7367,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="16">
       <c r="A8" s="16" t="s">
         <v>7</v>
       </c>
@@ -6935,7 +7390,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="16">
       <c r="A9" s="16" t="s">
         <v>7</v>
       </c>
@@ -6956,7 +7411,7 @@
       </c>
       <c r="G9" s="16"/>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="16">
       <c r="A10" s="16" t="s">
         <v>7</v>
       </c>
@@ -6977,7 +7432,7 @@
       </c>
       <c r="G10" s="16"/>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16">
       <c r="A11" s="16" t="s">
         <v>7</v>
       </c>
@@ -6998,7 +7453,7 @@
       </c>
       <c r="G11" s="16"/>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16">
       <c r="A12" s="16" t="s">
         <v>7</v>
       </c>
@@ -7019,7 +7474,7 @@
       </c>
       <c r="G12" s="16"/>
     </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="16">
       <c r="A13" s="16" t="s">
         <v>7</v>
       </c>
@@ -7040,7 +7495,7 @@
       </c>
       <c r="G13" s="16"/>
     </row>
-    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="16">
       <c r="A14" s="16" t="s">
         <v>7</v>
       </c>
@@ -7072,10 +7527,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -7085,40 +7540,40 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:7" ht="21">
+      <c r="A1" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-    </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="1:7" ht="16">
+      <c r="A2" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-    </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A3" s="35" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" spans="1:7" ht="16">
+      <c r="A3" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-    </row>
-    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.35">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+    </row>
+    <row r="5" spans="1:7" ht="33">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -7141,7 +7596,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="16">
       <c r="A6" s="17" t="s">
         <v>10</v>
       </c>
@@ -7162,7 +7617,7 @@
       </c>
       <c r="G6" s="17"/>
     </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="16">
       <c r="A7" s="17" t="s">
         <v>10</v>
       </c>
@@ -7183,7 +7638,7 @@
       </c>
       <c r="G7" s="17"/>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="16">
       <c r="A8" s="17" t="s">
         <v>10</v>
       </c>
@@ -7204,7 +7659,7 @@
       </c>
       <c r="G8" s="17"/>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="16">
       <c r="A9" s="17" t="s">
         <v>10</v>
       </c>
@@ -7225,7 +7680,7 @@
       </c>
       <c r="G9" s="17"/>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="16">
       <c r="A10" s="17" t="s">
         <v>10</v>
       </c>
@@ -7246,7 +7701,7 @@
       </c>
       <c r="G10" s="17"/>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16">
       <c r="A11" s="17" t="s">
         <v>10</v>
       </c>
@@ -7267,7 +7722,7 @@
       </c>
       <c r="G11" s="17"/>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16">
       <c r="A12" s="17" t="s">
         <v>10</v>
       </c>
@@ -7288,7 +7743,7 @@
       </c>
       <c r="G12" s="17"/>
     </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="16">
       <c r="A13" s="17" t="s">
         <v>10</v>
       </c>
@@ -7320,10 +7775,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -7333,40 +7788,40 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:7" ht="21">
+      <c r="A1" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-    </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="1:7" ht="16">
+      <c r="A2" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-    </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A3" s="35" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" spans="1:7" ht="16">
+      <c r="A3" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-    </row>
-    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.35">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+    </row>
+    <row r="5" spans="1:7" ht="33">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -7389,7 +7844,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="16">
       <c r="A6" s="18" t="s">
         <v>13</v>
       </c>
@@ -7410,7 +7865,7 @@
       </c>
       <c r="G6" s="18"/>
     </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="16">
       <c r="A7" s="18" t="s">
         <v>13</v>
       </c>
@@ -7431,7 +7886,7 @@
       </c>
       <c r="G7" s="18"/>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="16">
       <c r="A8" s="18" t="s">
         <v>13</v>
       </c>
@@ -7452,7 +7907,7 @@
       </c>
       <c r="G8" s="18"/>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="16">
       <c r="A9" s="18" t="s">
         <v>13</v>
       </c>
@@ -7473,7 +7928,7 @@
       </c>
       <c r="G9" s="18"/>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="16">
       <c r="A10" s="18" t="s">
         <v>13</v>
       </c>
@@ -7494,7 +7949,7 @@
       </c>
       <c r="G10" s="18"/>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16">
       <c r="A11" s="18" t="s">
         <v>13</v>
       </c>
@@ -7515,7 +7970,7 @@
       </c>
       <c r="G11" s="18"/>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16">
       <c r="A12" s="18" t="s">
         <v>13</v>
       </c>
@@ -7536,7 +7991,7 @@
       </c>
       <c r="G12" s="18"/>
     </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="16">
       <c r="A13" s="18" t="s">
         <v>13</v>
       </c>
@@ -7568,10 +8023,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -7581,40 +8036,40 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:7" ht="21">
+      <c r="A1" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-    </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="1:7" ht="16">
+      <c r="A2" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-    </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A3" s="35" t="s">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" spans="1:7" ht="16">
+      <c r="A3" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-    </row>
-    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.35">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+    </row>
+    <row r="5" spans="1:7" ht="33">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -7637,7 +8092,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="16">
       <c r="A6" s="19" t="s">
         <v>16</v>
       </c>
@@ -7658,7 +8113,7 @@
       </c>
       <c r="G6" s="19"/>
     </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="16">
       <c r="A7" s="19" t="s">
         <v>16</v>
       </c>
@@ -7679,7 +8134,7 @@
       </c>
       <c r="G7" s="19"/>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="16">
       <c r="A8" s="19" t="s">
         <v>16</v>
       </c>
@@ -7700,7 +8155,7 @@
       </c>
       <c r="G8" s="19"/>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="16">
       <c r="A9" s="19" t="s">
         <v>16</v>
       </c>
@@ -7721,7 +8176,7 @@
       </c>
       <c r="G9" s="19"/>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="16">
       <c r="A10" s="19" t="s">
         <v>16</v>
       </c>
@@ -7742,7 +8197,7 @@
       </c>
       <c r="G10" s="19"/>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16">
       <c r="A11" s="19" t="s">
         <v>16</v>
       </c>
@@ -7765,7 +8220,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16">
       <c r="A12" s="19" t="s">
         <v>16</v>
       </c>
@@ -7788,7 +8243,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="16">
       <c r="A13" s="19" t="s">
         <v>16</v>
       </c>
@@ -7809,7 +8264,7 @@
       </c>
       <c r="G13" s="19"/>
     </row>
-    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="16">
       <c r="A14" s="19" t="s">
         <v>16</v>
       </c>
@@ -7830,7 +8285,7 @@
       </c>
       <c r="G14" s="19"/>
     </row>
-    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="16">
       <c r="A15" s="19" t="s">
         <v>16</v>
       </c>
@@ -7851,7 +8306,7 @@
       </c>
       <c r="G15" s="19"/>
     </row>
-    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="16">
       <c r="A16" s="19" t="s">
         <v>16</v>
       </c>
@@ -7872,7 +8327,7 @@
       </c>
       <c r="G16" s="19"/>
     </row>
-    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="16">
       <c r="A17" s="19" t="s">
         <v>16</v>
       </c>
@@ -7902,277 +8357,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="39" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="6" width="32" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="36" t="s">
-        <v>132</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-    </row>
-    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A2" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-    </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.45">
-      <c r="A3" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-    </row>
-    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.35">
-      <c r="A6" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="20"/>
-    </row>
-    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.35">
-      <c r="A7" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.35">
-      <c r="A8" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="20"/>
-    </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.35">
-      <c r="A9" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="20"/>
-    </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.35">
-      <c r="A10" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="20"/>
-    </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.35">
-      <c r="A11" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.35">
-      <c r="A12" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="20"/>
-    </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.35">
-      <c r="A13" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13" s="20"/>
-    </row>
-    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.35">
-      <c r="A14" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14" s="20"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A5:G14" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
-  <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>